--- a/exports/trend_1d/HAVELLS_full_report.xlsx
+++ b/exports/trend_1d/HAVELLS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42034</v>
+        <v>42037</v>
       </c>
       <c r="H2" t="n">
-        <v>258.45</v>
+        <v>250.25</v>
       </c>
       <c r="I2" t="n">
         <v>256.1369494908</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.93</v>
+        <v>-6.01</v>
       </c>
       <c r="L2" t="n">
-        <v>3.34</v>
+        <v>6.29</v>
       </c>
       <c r="M2" t="n">
         <v>1.66</v>
       </c>
       <c r="N2" t="n">
-        <v>2.84</v>
+        <v>3.17</v>
       </c>
       <c r="O2" t="n">
         <v>0.99</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.34</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42058</v>
+        <v>42059</v>
       </c>
       <c r="H3" t="n">
-        <v>268.7</v>
+        <v>274.45</v>
       </c>
       <c r="I3" t="n">
         <v>273.7376328706597</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.37</v>
+        <v>-9.67</v>
       </c>
       <c r="L3" t="n">
         <v>10.65</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.22</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H4" t="n">
-        <v>279.55</v>
+        <v>269.45</v>
       </c>
       <c r="I4" t="n">
         <v>277.9219534525964</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K4" t="n">
-        <v>1.86</v>
+        <v>-1.82</v>
       </c>
       <c r="L4" t="n">
         <v>4.23</v>
@@ -669,7 +716,7 @@
         <v>0.51</v>
       </c>
       <c r="N4" t="n">
-        <v>3.19</v>
+        <v>3.61</v>
       </c>
       <c r="O4" t="n">
         <v>2.14</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.63</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42177</v>
+        <v>42178</v>
       </c>
       <c r="H5" t="n">
-        <v>286.25</v>
+        <v>290.95</v>
       </c>
       <c r="I5" t="n">
         <v>289.981189389127</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.23</v>
+        <v>-7.98</v>
       </c>
       <c r="L5" t="n">
         <v>9.44</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.19</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H6" t="n">
-        <v>298.05</v>
+        <v>283.05</v>
       </c>
       <c r="I6" t="n">
         <v>286.6954690178561</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>2.44</v>
+        <v>-2.72</v>
       </c>
       <c r="L6" t="n">
         <v>6.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>4.09</v>
+        <v>5.03</v>
       </c>
       <c r="O6" t="n">
         <v>1.64</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>10.88</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42318</v>
+        <v>42319</v>
       </c>
       <c r="H7" t="n">
-        <v>259.45</v>
+        <v>260.1</v>
       </c>
       <c r="I7" t="n">
         <v>259.7200550732056</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K7" t="n">
-        <v>8.34</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>2.46</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42381</v>
+        <v>42382</v>
       </c>
       <c r="H8" t="n">
-        <v>289.85</v>
+        <v>284.25</v>
       </c>
       <c r="I8" t="n">
         <v>286.532701544355</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K8" t="n">
-        <v>11.44</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>3.08</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.5</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42450</v>
+        <v>42451</v>
       </c>
       <c r="H9" t="n">
-        <v>299.55</v>
+        <v>303.9</v>
       </c>
       <c r="I9" t="n">
         <v>300.0321596180303</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.38</v>
+        <v>-6.91</v>
       </c>
       <c r="L9" t="n">
         <v>9.41</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.95</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42661</v>
+        <v>42662</v>
       </c>
       <c r="H10" t="n">
-        <v>431.85</v>
+        <v>409.15</v>
       </c>
       <c r="I10" t="n">
         <v>413.8103707945106</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K10" t="n">
-        <v>42.1</v>
+        <v>34.63</v>
       </c>
       <c r="L10" t="n">
         <v>1.6</v>
@@ -1011,7 +1130,7 @@
         <v>1.93</v>
       </c>
       <c r="N10" t="n">
-        <v>4.24</v>
+        <v>5.26</v>
       </c>
       <c r="O10" t="n">
         <v>1.45</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>13.02</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H11" t="n">
-        <v>351.15</v>
+        <v>359.55</v>
       </c>
       <c r="I11" t="n">
         <v>352.4803690397307</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K11" t="n">
-        <v>14.18</v>
+        <v>12.12</v>
       </c>
       <c r="L11" t="n">
         <v>6.07</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.42</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42789</v>
+        <v>42793</v>
       </c>
       <c r="H12" t="n">
-        <v>409.2</v>
+        <v>402.65</v>
       </c>
       <c r="I12" t="n">
         <v>408.9436254951041</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K12" t="n">
-        <v>13.81</v>
+        <v>11.99</v>
       </c>
       <c r="L12" t="n">
         <v>4.05</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42810</v>
+        <v>42811</v>
       </c>
       <c r="H13" t="n">
-        <v>436.1</v>
+        <v>442.7</v>
       </c>
       <c r="I13" t="n">
         <v>438.1819894830848</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.31</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>8.74</v>
+        <v>10.27</v>
       </c>
       <c r="M13" t="n">
         <v>1.4</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.14</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42874</v>
+        <v>42877</v>
       </c>
       <c r="H14" t="n">
-        <v>485.7</v>
+        <v>476.15</v>
       </c>
       <c r="I14" t="n">
         <v>479.6041345772646</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K14" t="n">
-        <v>9.710000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="L14" t="n">
         <v>1.49</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>10.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42891</v>
+        <v>42892</v>
       </c>
       <c r="H15" t="n">
-        <v>485.8</v>
+        <v>499.65</v>
       </c>
       <c r="I15" t="n">
         <v>498.2276309161239</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.03</v>
+        <v>-4.94</v>
       </c>
       <c r="L15" t="n">
-        <v>3.32</v>
+        <v>6.67</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>11.75</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42914</v>
+        <v>42915</v>
       </c>
       <c r="H16" t="n">
-        <v>462.4</v>
+        <v>449.55</v>
       </c>
       <c r="I16" t="n">
         <v>457.8219324543888</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.46</v>
+        <v>-10.03</v>
       </c>
       <c r="L16" t="n">
-        <v>9.34</v>
+        <v>10.69</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="n">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="O16" t="n">
         <v>2.85</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>11.55</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42951</v>
+        <v>42954</v>
       </c>
       <c r="H17" t="n">
-        <v>492.55</v>
+        <v>494.9</v>
       </c>
       <c r="I17" t="n">
         <v>493.7089682870536</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.57</v>
+        <v>-10.09</v>
       </c>
       <c r="L17" t="n">
-        <v>10.01</v>
+        <v>11.21</v>
       </c>
       <c r="M17" t="n">
         <v>0.95</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>6.87</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H18" t="n">
-        <v>463.65</v>
+        <v>458.65</v>
       </c>
       <c r="I18" t="n">
         <v>460.8921711292436</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.31</v>
+        <v>-7.32</v>
       </c>
       <c r="L18" t="n">
-        <v>8.220000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.35</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>6.89</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>11.34</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42993</v>
+        <v>42996</v>
       </c>
       <c r="H19" t="n">
-        <v>506.9</v>
+        <v>511.45</v>
       </c>
       <c r="I19" t="n">
         <v>510.6711165221033</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K19" t="n">
-        <v>-10.52</v>
+        <v>-11.51</v>
       </c>
       <c r="L19" t="n">
-        <v>12.68</v>
+        <v>12.69</v>
       </c>
       <c r="M19" t="n">
         <v>2</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.82</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H20" t="n">
-        <v>491.35</v>
+        <v>476.15</v>
       </c>
       <c r="I20" t="n">
         <v>480.8444702812873</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.93</v>
+        <v>-6.9</v>
       </c>
       <c r="L20" t="n">
-        <v>5.67</v>
+        <v>7.95</v>
       </c>
       <c r="M20" t="n">
         <v>0.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="O20" t="n">
         <v>0.9</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>10.33</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43017</v>
+        <v>43018</v>
       </c>
       <c r="H21" t="n">
-        <v>506.95</v>
+        <v>533.25</v>
       </c>
       <c r="I21" t="n">
         <v>518.0520901692424</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.47</v>
+        <v>-11.99</v>
       </c>
       <c r="L21" t="n">
-        <v>7.7</v>
+        <v>12.24</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.48</v>
+        <v>5.19</v>
       </c>
       <c r="O21" t="n">
         <v>-3.09</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>10.61</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43031</v>
+        <v>43032</v>
       </c>
       <c r="H22" t="n">
-        <v>541.45</v>
+        <v>503.4</v>
       </c>
       <c r="I22" t="n">
         <v>508.5790488043048</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
-        <v>1.54</v>
+        <v>-5.6</v>
       </c>
       <c r="L22" t="n">
-        <v>5.3</v>
+        <v>6.33</v>
       </c>
       <c r="M22" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="N22" t="n">
-        <v>1.09</v>
+        <v>7.03</v>
       </c>
       <c r="O22" t="n">
         <v>5.19</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>13.19</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43076</v>
+        <v>43077</v>
       </c>
       <c r="H23" t="n">
-        <v>525.75</v>
+        <v>537.1</v>
       </c>
       <c r="I23" t="n">
         <v>534.6564714715461</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.44</v>
+        <v>-6.69</v>
       </c>
       <c r="L23" t="n">
-        <v>6.65</v>
+        <v>7.27</v>
       </c>
       <c r="M23" t="n">
         <v>1.62</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.15</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43130</v>
+        <v>43131</v>
       </c>
       <c r="H24" t="n">
-        <v>552.85</v>
+        <v>522.35</v>
       </c>
       <c r="I24" t="n">
         <v>534.8827746503382</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K24" t="n">
-        <v>2.93</v>
+        <v>-2.75</v>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>3.54</v>
       </c>
       <c r="M24" t="n">
-        <v>0.74</v>
+        <v>2.32</v>
       </c>
       <c r="N24" t="n">
-        <v>3.94</v>
+        <v>5.52</v>
       </c>
       <c r="O24" t="n">
         <v>2.16</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.05</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43195</v>
+        <v>43196</v>
       </c>
       <c r="H25" t="n">
-        <v>512.65</v>
+        <v>533.15</v>
       </c>
       <c r="I25" t="n">
         <v>523.7249198783047</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K25" t="n">
-        <v>1.86</v>
+        <v>-2.07</v>
       </c>
       <c r="L25" t="n">
         <v>3.38</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H26" t="n">
-        <v>668.8</v>
+        <v>660.4</v>
       </c>
       <c r="I26" t="n">
         <v>667.8926694400875</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K26" t="n">
-        <v>25.44</v>
+        <v>23.87</v>
       </c>
       <c r="L26" t="n">
         <v>3.85</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.24</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43416</v>
+        <v>43417</v>
       </c>
       <c r="H27" t="n">
-        <v>651.1</v>
+        <v>666.15</v>
       </c>
       <c r="I27" t="n">
         <v>652.8928578418562</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K27" t="n">
-        <v>1.41</v>
+        <v>-0.87</v>
       </c>
       <c r="L27" t="n">
         <v>3.57</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.7</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43510</v>
+        <v>43511</v>
       </c>
       <c r="H28" t="n">
-        <v>694.15</v>
+        <v>688.65</v>
       </c>
       <c r="I28" t="n">
         <v>690.5018107273817</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="L28" t="n">
         <v>2.72</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.17</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H29" t="n">
-        <v>727.85</v>
+        <v>742.6</v>
       </c>
       <c r="I29" t="n">
         <v>737.5950190302295</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.69</v>
+        <v>-7.83</v>
       </c>
       <c r="L29" t="n">
-        <v>6.14</v>
+        <v>8.33</v>
       </c>
       <c r="M29" t="n">
         <v>0.63</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>8.19</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H30" t="n">
-        <v>739</v>
+        <v>732.25</v>
       </c>
       <c r="I30" t="n">
         <v>734.0989955619341</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.48</v>
+        <v>-1.39</v>
       </c>
       <c r="L30" t="n">
         <v>2.42</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>6.6</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43616</v>
+        <v>43619</v>
       </c>
       <c r="H31" t="n">
-        <v>747.95</v>
+        <v>769.95</v>
       </c>
       <c r="I31" t="n">
         <v>766.5769785678385</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.14</v>
+        <v>-5.15</v>
       </c>
       <c r="L31" t="n">
-        <v>5.01</v>
+        <v>5.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.69</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H32" t="n">
-        <v>746.55</v>
+        <v>738.85</v>
       </c>
       <c r="I32" t="n">
         <v>746.4592421722455</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.04</v>
+        <v>-4.04</v>
       </c>
       <c r="L32" t="n">
-        <v>3.61</v>
+        <v>5.97</v>
       </c>
       <c r="M32" t="n">
         <v>1.03</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.13</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H33" t="n">
-        <v>645.05</v>
+        <v>727.65</v>
       </c>
       <c r="I33" t="n">
         <v>700.2089950741009</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K33" t="n">
-        <v>12.7</v>
+        <v>1.52</v>
       </c>
       <c r="L33" t="n">
         <v>1.78</v>
@@ -2322,7 +2717,7 @@
         <v>2.75</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>12.81</v>
       </c>
       <c r="O33" t="n">
         <v>-1.03</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>16.56</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43749</v>
+        <v>43752</v>
       </c>
       <c r="H34" t="n">
-        <v>660.7</v>
+        <v>653.9</v>
       </c>
       <c r="I34" t="n">
         <v>656.5279639899783</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K34" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.14</v>
       </c>
       <c r="L34" t="n">
         <v>12.24</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>11.21</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43885</v>
+        <v>43886</v>
       </c>
       <c r="H35" t="n">
-        <v>626.65</v>
+        <v>643.6</v>
       </c>
       <c r="I35" t="n">
         <v>640.5462451381331</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K35" t="n">
-        <v>4.17</v>
+        <v>1.58</v>
       </c>
       <c r="L35" t="n">
         <v>9.69</v>
       </c>
       <c r="M35" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="N35" t="n">
         <v>4.16</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.18</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H36" t="n">
-        <v>613.2</v>
+        <v>578.7</v>
       </c>
       <c r="I36" t="n">
         <v>595.8165229583838</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.72</v>
+        <v>-10.08</v>
       </c>
       <c r="L36" t="n">
-        <v>7.82</v>
+        <v>20.04</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="N36" t="n">
-        <v>4.02</v>
+        <v>5.63</v>
       </c>
       <c r="O36" t="n">
         <v>2.7</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>11.24</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H37" t="n">
-        <v>496.25</v>
+        <v>540.35</v>
       </c>
       <c r="I37" t="n">
         <v>530.583233636779</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K37" t="n">
-        <v>14.25</v>
+        <v>6.63</v>
       </c>
       <c r="L37" t="n">
         <v>7.73</v>
@@ -2550,7 +2993,7 @@
         <v>2.97</v>
       </c>
       <c r="N37" t="n">
-        <v>6.38</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="O37" t="n">
         <v>-5.63</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>17.78</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H38" t="n">
-        <v>1088.45</v>
+        <v>1061.8</v>
       </c>
       <c r="I38" t="n">
         <v>1069.217453221552</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K38" t="n">
-        <v>101.43</v>
+        <v>96.5</v>
       </c>
       <c r="L38" t="n">
         <v>7.09</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>202</v>
+        <v>203</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>10</v>
+      </c>
+      <c r="U38" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.69</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44392</v>
+        <v>44393</v>
       </c>
       <c r="H39" t="n">
-        <v>1039.85</v>
+        <v>1077.65</v>
       </c>
       <c r="I39" t="n">
         <v>1048.588576549722</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K39" t="n">
-        <v>2.07</v>
+        <v>-1.49</v>
       </c>
       <c r="L39" t="n">
         <v>3.59</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>7.61</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H40" t="n">
-        <v>1406.7</v>
+        <v>1285.8</v>
       </c>
       <c r="I40" t="n">
         <v>1358.729967477542</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K40" t="n">
-        <v>30.53</v>
+        <v>19.32</v>
       </c>
       <c r="L40" t="n">
         <v>3.12</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>4.86</v>
+        <v>8.59</v>
       </c>
       <c r="O40" t="n">
         <v>3.64</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>14.78</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H41" t="n">
-        <v>1397</v>
+        <v>1406.15</v>
       </c>
       <c r="I41" t="n">
         <v>1401.519828825483</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.65</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="L41" t="n">
         <v>11.17</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>6.83</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44579</v>
+        <v>44580</v>
       </c>
       <c r="H42" t="n">
-        <v>1315.45</v>
+        <v>1308.75</v>
       </c>
       <c r="I42" t="n">
         <v>1310.057194137937</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.45</v>
+        <v>-6.93</v>
       </c>
       <c r="L42" t="n">
-        <v>6.77</v>
+        <v>7.98</v>
       </c>
       <c r="M42" t="n">
         <v>0.71</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44655</v>
+        <v>44656</v>
       </c>
       <c r="H43" t="n">
-        <v>1180.3</v>
+        <v>1258.65</v>
       </c>
       <c r="I43" t="n">
         <v>1194.672043216146</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K43" t="n">
-        <v>9.81</v>
+        <v>3.83</v>
       </c>
       <c r="L43" t="n">
         <v>1.83</v>
@@ -2892,7 +3407,7 @@
         <v>2.05</v>
       </c>
       <c r="N43" t="n">
-        <v>5.02</v>
+        <v>6.64</v>
       </c>
       <c r="O43" t="n">
         <v>-0.51</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.78</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H44" t="n">
-        <v>1238.55</v>
+        <v>1215.5</v>
       </c>
       <c r="I44" t="n">
         <v>1231.728482819183</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.6</v>
+        <v>-3.43</v>
       </c>
       <c r="L44" t="n">
         <v>5.96</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44747</v>
+        <v>44748</v>
       </c>
       <c r="H45" t="n">
-        <v>1157.1</v>
+        <v>1197.2</v>
       </c>
       <c r="I45" t="n">
         <v>1181.938984477383</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K45" t="n">
-        <v>4.8</v>
+        <v>1.51</v>
       </c>
       <c r="L45" t="n">
         <v>4.99</v>
@@ -3006,7 +3545,7 @@
         <v>2.04</v>
       </c>
       <c r="N45" t="n">
-        <v>3.24</v>
+        <v>3.47</v>
       </c>
       <c r="O45" t="n">
         <v>-1.86</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.31</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44844</v>
+        <v>44845</v>
       </c>
       <c r="H46" t="n">
-        <v>1345.4</v>
+        <v>1279.4</v>
       </c>
       <c r="I46" t="n">
         <v>1286.563736372279</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K46" t="n">
-        <v>12.38</v>
+        <v>6.87</v>
       </c>
       <c r="L46" t="n">
         <v>3.19</v>
@@ -3063,7 +3614,7 @@
         <v>2.69</v>
       </c>
       <c r="N46" t="n">
-        <v>4.66</v>
+        <v>4.91</v>
       </c>
       <c r="O46" t="n">
         <v>3.47</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>11.69</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44931</v>
+        <v>44932</v>
       </c>
       <c r="H47" t="n">
-        <v>1167.1</v>
+        <v>1192.5</v>
       </c>
       <c r="I47" t="n">
         <v>1181.246762420186</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K47" t="n">
-        <v>8.779999999999999</v>
+        <v>6.79</v>
       </c>
       <c r="L47" t="n">
         <v>5.69</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.87</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45012</v>
+        <v>45013</v>
       </c>
       <c r="H48" t="n">
-        <v>1167.9</v>
+        <v>1144</v>
       </c>
       <c r="I48" t="n">
         <v>1145.450698618854</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.06</v>
+        <v>-4.07</v>
       </c>
       <c r="L48" t="n">
-        <v>4.69</v>
+        <v>5.09</v>
       </c>
       <c r="M48" t="n">
         <v>0.55</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>7.73</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45048</v>
+        <v>45049</v>
       </c>
       <c r="H49" t="n">
-        <v>1225.6</v>
+        <v>1241.3</v>
       </c>
       <c r="I49" t="n">
         <v>1232.396228767209</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K49" t="n">
-        <v>-7.13</v>
+        <v>-8.51</v>
       </c>
       <c r="L49" t="n">
-        <v>8.65</v>
+        <v>9.27</v>
       </c>
       <c r="M49" t="n">
         <v>0.51</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.76</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="H50" t="n">
-        <v>1325.4</v>
+        <v>1284.95</v>
       </c>
       <c r="I50" t="n">
         <v>1288.322934791629</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K50" t="n">
-        <v>6.78</v>
+        <v>3.52</v>
       </c>
       <c r="L50" t="n">
         <v>2.37</v>
@@ -3291,7 +3890,7 @@
         <v>0.38</v>
       </c>
       <c r="N50" t="n">
-        <v>2.17</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
         <v>1.28</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>7.74</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45125</v>
+        <v>45126</v>
       </c>
       <c r="H51" t="n">
-        <v>1334.4</v>
+        <v>1364</v>
       </c>
       <c r="I51" t="n">
         <v>1358.308179455239</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.85</v>
+        <v>-6.15</v>
       </c>
       <c r="L51" t="n">
-        <v>6.77</v>
+        <v>7.79</v>
       </c>
       <c r="M51" t="n">
         <v>2.19</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.71</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45216</v>
+        <v>45217</v>
       </c>
       <c r="H52" t="n">
-        <v>1384.05</v>
+        <v>1340.35</v>
       </c>
       <c r="I52" t="n">
         <v>1356.002326231614</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K52" t="n">
-        <v>1.47</v>
+        <v>-1.73</v>
       </c>
       <c r="L52" t="n">
         <v>7.41</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.5</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="H53" t="n">
-        <v>1317.55</v>
+        <v>1324.45</v>
       </c>
       <c r="I53" t="n">
         <v>1322.857039855931</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K53" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="L53" t="n">
         <v>3.26</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>3.98</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H54" t="n">
-        <v>1375.6</v>
+        <v>1313.15</v>
       </c>
       <c r="I54" t="n">
         <v>1345.404435477707</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K54" t="n">
-        <v>3.86</v>
+        <v>-0.85</v>
       </c>
       <c r="L54" t="n">
-        <v>1.05</v>
+        <v>1.8</v>
       </c>
       <c r="M54" t="n">
         <v>0.48</v>
       </c>
       <c r="N54" t="n">
-        <v>2.68</v>
+        <v>4.54</v>
       </c>
       <c r="O54" t="n">
         <v>0.52</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.11</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="H55" t="n">
-        <v>1380.65</v>
+        <v>1399.1</v>
       </c>
       <c r="I55" t="n">
         <v>1396.367725256842</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.14</v>
+        <v>-6.55</v>
       </c>
       <c r="L55" t="n">
-        <v>5.95</v>
+        <v>6.69</v>
       </c>
       <c r="M55" t="n">
         <v>0.79</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.81</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H56" t="n">
-        <v>1862.65</v>
+        <v>1768.5</v>
       </c>
       <c r="I56" t="n">
         <v>1786.494825609479</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K56" t="n">
-        <v>33.13</v>
+        <v>26.4</v>
       </c>
       <c r="L56" t="n">
         <v>1.48</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>6</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>13.57</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45524</v>
+        <v>45525</v>
       </c>
       <c r="H57" t="n">
-        <v>1889.7</v>
+        <v>1920.55</v>
       </c>
       <c r="I57" t="n">
         <v>1914.379915794946</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.85</v>
+        <v>-8.6</v>
       </c>
       <c r="L57" t="n">
-        <v>7.58</v>
+        <v>8.85</v>
       </c>
       <c r="M57" t="n">
         <v>1.36</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.31</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H58" t="n">
-        <v>1972.9</v>
+        <v>1934.45</v>
       </c>
       <c r="I58" t="n">
         <v>1949.160036454879</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K58" t="n">
-        <v>2.73</v>
+        <v>0.72</v>
       </c>
       <c r="L58" t="n">
         <v>3.2</v>
@@ -3747,7 +4442,7 @@
         <v>2.04</v>
       </c>
       <c r="N58" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O58" t="n">
         <v>1.63</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H59" t="n">
-        <v>1739.35</v>
+        <v>1757.2</v>
       </c>
       <c r="I59" t="n">
         <v>1740.896876731296</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K59" t="n">
-        <v>10.09</v>
+        <v>9.16</v>
       </c>
       <c r="L59" t="n">
         <v>2.54</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.98</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H60" t="n">
-        <v>1693.15</v>
+        <v>1657.4</v>
       </c>
       <c r="I60" t="n">
         <v>1658.793772329286</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.65</v>
+        <v>-5.68</v>
       </c>
       <c r="L60" t="n">
-        <v>4.67</v>
+        <v>6.1</v>
       </c>
       <c r="M60" t="n">
         <v>0.77</v>
       </c>
       <c r="N60" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="O60" t="n">
         <v>1.03</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H61" t="n">
-        <v>1566.2</v>
+        <v>1656.2</v>
       </c>
       <c r="I61" t="n">
         <v>1646.361784633209</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K61" t="n">
-        <v>5.5</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L61" t="n">
         <v>3.85</v>
@@ -3918,7 +4649,7 @@
         <v>1.64</v>
       </c>
       <c r="N61" t="n">
-        <v>2.68</v>
+        <v>5.75</v>
       </c>
       <c r="O61" t="n">
         <v>-2.11</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>12.93</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H62" t="n">
-        <v>1522.55</v>
+        <v>1498.25</v>
       </c>
       <c r="I62" t="n">
         <v>1503.647352541937</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>-8.07</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>8.949999999999999</v>
+        <v>10.04</v>
       </c>
       <c r="M62" t="n">
         <v>0.68</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>11.81</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H63" t="n">
-        <v>1532.85</v>
+        <v>1571.7</v>
       </c>
       <c r="I63" t="n">
         <v>1567.382442493884</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.31</v>
+        <v>-4.9</v>
       </c>
       <c r="L63" t="n">
-        <v>4.59</v>
+        <v>5.3</v>
       </c>
       <c r="M63" t="n">
         <v>1.14</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>11.7</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45807</v>
+        <v>45810</v>
       </c>
       <c r="H64" t="n">
-        <v>1527</v>
+        <v>1514.8</v>
       </c>
       <c r="I64" t="n">
         <v>1520.244241215172</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.84</v>
+        <v>-3.62</v>
       </c>
       <c r="L64" t="n">
         <v>4.59</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.33</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45818</v>
+        <v>45819</v>
       </c>
       <c r="H65" t="n">
-        <v>1569.6</v>
+        <v>1579.1</v>
       </c>
       <c r="I65" t="n">
         <v>1576.856954002358</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.62</v>
+        <v>-4.24</v>
       </c>
       <c r="L65" t="n">
         <v>4.55</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>5.65</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H66" t="n">
-        <v>1500.6</v>
+        <v>1482.6</v>
       </c>
       <c r="I66" t="n">
         <v>1489.949237479052</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.97</v>
+        <v>-6.11</v>
       </c>
       <c r="L66" t="n">
-        <v>5.94</v>
+        <v>6.53</v>
       </c>
       <c r="M66" t="n">
         <v>4.59</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.77</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="H67" t="n">
-        <v>1552.6</v>
+        <v>1570</v>
       </c>
       <c r="I67" t="n">
         <v>1557.482893934346</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.72</v>
+        <v>-5.9</v>
       </c>
       <c r="L67" t="n">
         <v>6.7</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>7.78</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H68" t="n">
-        <v>1539.6</v>
+        <v>1507.4</v>
       </c>
       <c r="I68" t="n">
         <v>1524.914066258385</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.94</v>
+        <v>-3.99</v>
       </c>
       <c r="L68" t="n">
-        <v>3.89</v>
+        <v>4.39</v>
       </c>
       <c r="M68" t="n">
         <v>0.61</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.18</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H69" t="n">
-        <v>1451.4</v>
+        <v>1501.7</v>
       </c>
       <c r="I69" t="n">
         <v>1468.856434963958</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K69" t="n">
-        <v>3.72</v>
+        <v>0.38</v>
       </c>
       <c r="L69" t="n">
         <v>2.08</v>
@@ -4374,7 +5201,7 @@
         <v>0.7</v>
       </c>
       <c r="N69" t="n">
-        <v>1.95</v>
+        <v>3.47</v>
       </c>
       <c r="O69" t="n">
         <v>-2.09</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>7</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H70" t="n">
-        <v>1447.1</v>
+        <v>1346.3</v>
       </c>
       <c r="I70" t="n">
         <v>1419.990761810198</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.64</v>
+        <v>-10.35</v>
       </c>
       <c r="L70" t="n">
-        <v>5.57</v>
+        <v>10.95</v>
       </c>
       <c r="M70" t="n">
-        <v>0.82</v>
+        <v>1.46</v>
       </c>
       <c r="N70" t="n">
-        <v>1.29</v>
+        <v>6.97</v>
       </c>
       <c r="O70" t="n">
         <v>3.47</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>12.32</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H71" t="n">
-        <v>1373.1</v>
+        <v>1383.8</v>
       </c>
       <c r="I71" t="n">
         <v>1374.843261756087</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K71" t="n">
-        <v>-1.99</v>
+        <v>-2.79</v>
       </c>
       <c r="L71" t="n">
         <v>8.039999999999999</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>7.94</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H72" t="n">
-        <v>1354</v>
+        <v>1318.7</v>
       </c>
       <c r="I72" t="n">
         <v>1337.705876450369</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K72" t="n">
-        <v>-2.15</v>
+        <v>-4.7</v>
       </c>
       <c r="L72" t="n">
-        <v>3.62</v>
+        <v>5.04</v>
       </c>
       <c r="M72" t="n">
         <v>2.66</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>8.19</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H73" t="n">
-        <v>1291.1</v>
+        <v>1306.4</v>
       </c>
       <c r="I73" t="n">
         <v>1300.188799918664</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K73" t="n">
-        <v>2.09</v>
+        <v>0.93</v>
       </c>
       <c r="L73" t="n">
         <v>6.51</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>9.98</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H74" t="n">
-        <v>1255.2</v>
+        <v>1230</v>
       </c>
       <c r="I74" t="n">
         <v>1231.710380484634</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.92</v>
+        <v>-5.85</v>
       </c>
       <c r="L74" t="n">
-        <v>5.77</v>
+        <v>6.11</v>
       </c>
       <c r="M74" t="n">
         <v>4.01</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>8.82</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="H75" t="n">
-        <v>1209.9</v>
+        <v>1226.9</v>
       </c>
       <c r="I75" t="n">
         <v>1225.633002253359</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K75" t="n">
-        <v>1.63</v>
+        <v>0.25</v>
       </c>
       <c r="L75" t="n">
         <v>1.54</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>8.33</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="H76" t="n">
-        <v>1241</v>
+        <v>1222.9</v>
       </c>
       <c r="I76" t="n">
         <v>1225.6365506567</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K76" t="n">
-        <v>1.15</v>
+        <v>-0.33</v>
       </c>
       <c r="L76" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="M76" t="n">
         <v>0.73</v>
       </c>
       <c r="N76" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="O76" t="n">
         <v>1.41</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>6.56</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H77" t="n">
-        <v>1082</v>
+        <v>1119.9</v>
       </c>
       <c r="I77" t="n">
         <v>1111.499247177428</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K77" t="n">
-        <v>11.52</v>
+        <v>8.42</v>
       </c>
       <c r="L77" t="n">
         <v>1.97</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>9.82</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H78" t="n">
-        <v>1073</v>
+        <v>1031</v>
       </c>
       <c r="I78" t="n">
         <v>1039.9941200342</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K78" t="n">
-        <v>-4.19</v>
+        <v>-7.94</v>
       </c>
       <c r="L78" t="n">
-        <v>6.42</v>
+        <v>10.46</v>
       </c>
       <c r="M78" t="n">
         <v>0.24</v>
       </c>
       <c r="N78" t="n">
-        <v>2.82</v>
+        <v>3.91</v>
       </c>
       <c r="O78" t="n">
         <v>3.5</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>4</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.3</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.01</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.78</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.16</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>101.43</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.1</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.35</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.99</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="21">
@@ -10065,7 +11020,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.68</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="22">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="25">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.65</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="27">
@@ -10125,7 +11080,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.59</v>
+        <v>12.81</v>
       </c>
     </row>
     <row r="28">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
